--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/Echo_Chapter1.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/Echo_Chapter1.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -1684,6 +1684,9 @@
       <c r="A35" s="1">
         <v>34</v>
       </c>
+      <c r="B35" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G35" s="2" t="s">
         <v>61</v>
       </c>
@@ -1703,6 +1706,9 @@
       <c r="A37" s="1">
         <v>36</v>
       </c>
+      <c r="B37" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G37" s="2" t="s">
         <v>63</v>
       </c>
@@ -1713,6 +1719,9 @@
     <row r="38" ht="27.6" spans="1:11">
       <c r="A38" s="1">
         <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>65</v>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/Echo_Chapter1.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/Echo_Chapter1.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
   <si>
     <t>ID</t>
   </si>
@@ -76,6 +76,9 @@
     <t>世界从未安静过。</t>
   </si>
   <si>
+    <t>chaptercard(序曲,失谐,2.0)</t>
+  </si>
+  <si>
     <t>每一种情绪，都有它的频率。</t>
   </si>
   <si>
@@ -94,7 +97,8 @@
     <t>冷夜。</t>
   </si>
   <si>
-    <t>bgfade(prelude_01,2)</t>
+    <t>chaptercard(第一章,未署名的求救信号,2.0)
+&amp;bgfade(prelude_01,2)</t>
   </si>
   <si>
     <t>今夜的城市，依旧灯火通明。</t>
@@ -226,14 +230,13 @@
     <t>她按下播放键。一阵清澈、简单却莫名忧伤的八音盒旋律流淌出来。</t>
   </si>
   <si>
-    <t>chapter(complete,CH01)&amp;
-autosave()</t>
-  </si>
-  <si>
     <t>伴随着八音盒清脆的“叮——”声，保险柜内部发出一声沉闷的机械解锁声。</t>
   </si>
   <si>
     <t>紧接着，不是预想中的开门声，而是一阵令人牙酸的金属撕裂声。</t>
+  </si>
+  <si>
+    <t>浓稠的黑色雾气如同高压锅泄气般从门缝里喷涌而出。原本微弱的冷光被迅速吞噬，紧接着地下室的温度骤降。</t>
   </si>
 </sst>
 </file>
@@ -869,19 +872,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1213,7 +1222,7 @@
     <col min="8" max="8" width="17.75" style="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" customWidth="1"/>
     <col min="10" max="10" width="15.0462962962963" style="1" customWidth="1"/>
-    <col min="11" max="11" width="30.2222222222222" style="1" customWidth="1"/>
+    <col min="11" max="11" width="43.8981481481481" style="1" customWidth="1"/>
     <col min="12" max="12" width="21.6481481481481" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
@@ -1237,7 +1246,7 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -1266,6 +1275,9 @@
       <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1">
@@ -1275,7 +1287,7 @@
         <v>12</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1286,7 +1298,7 @@
         <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1297,7 +1309,7 @@
         <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1308,7 +1320,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1319,11 +1331,11 @@
         <v>12</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="4"/>
-    </row>
-    <row r="8" spans="1:12">
+        <v>19</v>
+      </c>
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" ht="26.4" spans="1:12">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1331,10 +1343,10 @@
         <v>12</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="4" t="s">
         <v>20</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1345,12 +1357,12 @@
         <v>12</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" ht="27.6" spans="1:12">
       <c r="A10" s="1">
@@ -1360,12 +1372,12 @@
         <v>12</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="4"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" ht="41.4" spans="1:12">
       <c r="A11" s="1">
@@ -1375,25 +1387,25 @@
         <v>12</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K11" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" ht="27.6" spans="1:12">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="4" t="s">
         <v>27</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="27.6" spans="1:12">
@@ -1401,13 +1413,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="41.4" spans="1:12">
@@ -1415,13 +1427,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="15" ht="27.6" spans="1:12">
@@ -1429,13 +1441,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:12">
@@ -1446,10 +1458,10 @@
         <v>12</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1460,10 +1472,10 @@
         <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1471,13 +1483,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K18" s="4" t="s">
         <v>37</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="19" ht="27.6" spans="1:11">
@@ -1488,10 +1500,10 @@
         <v>12</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="4" t="s">
         <v>39</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1" spans="1:11">
@@ -1502,10 +1514,10 @@
         <v>12</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="4" t="s">
         <v>41</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21" ht="27.6" spans="1:11">
@@ -1516,10 +1528,10 @@
         <v>12</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1527,13 +1539,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="23" ht="27.6" spans="1:11">
@@ -1544,10 +1556,10 @@
         <v>12</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" ht="27.6" spans="1:11">
@@ -1555,13 +1567,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1572,10 +1584,10 @@
         <v>12</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1583,10 +1595,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1594,10 +1606,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1605,10 +1617,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1616,10 +1628,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" ht="27.6" spans="1:11">
@@ -1630,7 +1642,7 @@
         <v>12</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1638,13 +1650,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" ht="41.4" spans="1:11">
@@ -1655,10 +1667,10 @@
         <v>12</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1666,21 +1678,21 @@
         <v>12</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1688,21 +1700,21 @@
         <v>12</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" ht="27.6" spans="1:11">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1710,13 +1722,10 @@
         <v>12</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K37" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="38" ht="27.6" spans="1:11">
+    <row r="38" ht="27.6" spans="1:7">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1727,50 +1736,62 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <v>38</v>
       </c>
+      <c r="B39" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G39" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" ht="27.6" spans="1:7">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:11">
+      <c r="B40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:11">
+      <c r="G41" s="2">
+        <v>123123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <v>46</v>
       </c>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/Echo_Chapter1.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/Echo_Chapter1.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
   <si>
     <t>ID</t>
   </si>
@@ -221,7 +221,7 @@
     <t>这是什么邪典机关？放首歌才能打开？</t>
   </si>
   <si>
-    <t>这时，队长走上前，从口袋里拿出一个MP3播放器，连接到唱针接口。</t>
+    <t>这时，队长走上前，从口袋里掏出一个MP3播放器，连接到唱针接口。</t>
   </si>
   <si>
     <t>不，是需要一段正确的旋律来解锁。</t>
@@ -237,6 +237,33 @@
   </si>
   <si>
     <t>浓稠的黑色雾气如同高压锅泄气般从门缝里喷涌而出。原本微弱的冷光被迅速吞噬，紧接着地下室的温度骤降。</t>
+  </si>
+  <si>
+    <t>咳咳……见鬼，老K到底发的什么情报！这哪是迷路的灵魂，这是个积怨已久的炸药包！</t>
+  </si>
+  <si>
+    <t>此刻小满正紧盯着探测器，只见屏幕上的波形已经红到发紫，像着了魔一样疯狂跳动。</t>
+  </si>
+  <si>
+    <t>队长！这不是单纯的残留情绪，它已经具象化了！共鸣等级…… C级，不，还在上升！B级！而且……</t>
+  </si>
+  <si>
+    <t>她抬起头，看向空中那团狂躁的黑雾。</t>
+  </si>
+  <si>
+    <t>它的核心频率是……极度焦虑与自我否定！</t>
+  </si>
+  <si>
+    <t>黑雾在半空中扭曲、聚合，最终化作一个庞大的，如同由无数废弃乐谱和病历单拼凑而成的畸形怪物。怪物的头部是一个巨大的、指针疯狂乱转的节拍器。</t>
+  </si>
+  <si>
+    <t>怪物</t>
+  </si>
+  <si>
+    <t>不够……还不够完美……错了一个音……全部重来……全部毁掉！！！</t>
+  </si>
+  <si>
+    <t>shake(dialogue,1.0,10)</t>
   </si>
 </sst>
 </file>
@@ -883,14 +910,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1246,7 +1273,7 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -1333,7 +1360,7 @@
       <c r="G7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7" s="4"/>
     </row>
     <row r="8" ht="26.4" spans="1:12">
       <c r="A8" s="1">
@@ -1345,7 +1372,7 @@
       <c r="G8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1362,7 +1389,7 @@
       <c r="H9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="5"/>
+      <c r="K9" s="4"/>
     </row>
     <row r="10" ht="27.6" spans="1:12">
       <c r="A10" s="1">
@@ -1377,7 +1404,7 @@
       <c r="H10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="4"/>
     </row>
     <row r="11" ht="41.4" spans="1:12">
       <c r="A11" s="1">
@@ -1392,7 +1419,7 @@
       <c r="H11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="5"/>
+      <c r="K11" s="4"/>
     </row>
     <row r="12" ht="27.6" spans="1:12">
       <c r="A12" s="1">
@@ -1404,7 +1431,7 @@
       <c r="G12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1488,7 +1515,7 @@
       <c r="G18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="4" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1502,7 +1529,7 @@
       <c r="G19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="4" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1516,7 +1543,7 @@
       <c r="G20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1670,7 +1697,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:11">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1681,7 +1708,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:11">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1692,7 +1719,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:11">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1703,7 +1730,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:11">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1714,7 +1741,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:11">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1725,7 +1752,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" ht="27.6" spans="1:7">
+    <row r="38" ht="27.6" spans="1:11">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1736,7 +1763,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:11">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1747,7 +1774,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" ht="27.6" spans="1:7">
+    <row r="40" ht="27.6" spans="1:11">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1758,42 +1785,84 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" ht="27.6" spans="1:11">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="G41" s="2">
-        <v>123123</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="B41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" ht="27.6" spans="1:11">
       <c r="A42" s="1">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="B42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" ht="27.6" spans="1:11">
       <c r="A43" s="1">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="B43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="B44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="1">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="B45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" ht="41.4" spans="1:11">
       <c r="A46" s="1">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="B46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="1">
         <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G47" t="s">
+        <v>75</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
